--- a/output/upload/S00027_2236_스마트V상해보험_무배당.xlsx
+++ b/output/upload/S00027_2236_스마트V상해보험_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2236006</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22366</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2236006</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22366</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2236006</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22366</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2236006</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22366</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2236006</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22366</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00027_2236_스마트V상해보험_무배당.xlsx
+++ b/output/upload/S00027_2236_스마트V상해보험_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>2236006</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>2236006</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>2236006</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>2236006</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>2236006</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">

--- a/output/upload/S00027_2236_스마트V상해보험_무배당.xlsx
+++ b/output/upload/S00027_2236_스마트V상해보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3126,20 +3126,72 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2236007</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 2형(보장강화형)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2236007</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 2형(보장강화형)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>X110</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n"/>
@@ -3177,20 +3229,72 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-      <c r="M13" s="6" t="n"/>
-      <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2236007</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 2형(보장강화형)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2236007</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 2형(보장강화형)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>X110</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P13" s="6" t="n"/>
       <c r="Q13" s="6" t="n"/>
       <c r="R13" s="6" t="n"/>
@@ -3228,20 +3332,72 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2236007</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 2형(보장강화형)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2236007</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 2형(보장강화형)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>X110</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="6" t="n"/>
@@ -3277,6 +3433,142 @@
       <c r="AV14" s="6" t="n"/>
       <c r="AW14" s="6" t="n"/>
     </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2236007</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 2형(보장강화형)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2236007</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 2형(보장강화형)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X110</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>110</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>15</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2236007</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 2형(보장강화형)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2236007</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V상해보험 무배당 1종 2형(보장강화형)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X110</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>110</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>20</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="I3:N3"/>

--- a/output/upload/S00027_2236_스마트V상해보험_무배당.xlsx
+++ b/output/upload/S00027_2236_스마트V상해보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
